--- a/SuppXLS/Scen_B_SYS_MaxGrowthRates.xlsx
+++ b/SuppXLS/Scen_B_SYS_MaxGrowthRates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\TIM-LEAF\tim-leaf v1.3BS\tim-leaf v1.3BS\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94767615-02FA-46B7-B69C-D3204EB09039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3EAC24-7F0E-4156-B7ED-A1C127548EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{39DC52AD-7AD8-48BE-9D85-AA1C40791A2D}"/>
+    <workbookView xWindow="15120" yWindow="-16310" windowWidth="29020" windowHeight="15700" activeTab="4" xr2:uid="{39DC52AD-7AD8-48BE-9D85-AA1C40791A2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="6" r:id="rId1"/>
@@ -6126,8 +6126,8 @@
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>68792</xdr:rowOff>
     </xdr:to>
@@ -11292,8 +11292,8 @@
         <v>1</v>
       </c>
       <c r="H27" s="61">
-        <f>H26</f>
-        <v>0.70799999999999996</v>
+        <f>5.11-5.06</f>
+        <v>5.0000000000000711E-2</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -11338,8 +11338,8 @@
         <v>1</v>
       </c>
       <c r="H29" s="61">
-        <f>H28+0.2</f>
-        <v>0.86499999999999999</v>
+        <f>6.4-5.755</f>
+        <v>0.64500000000000046</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -11361,8 +11361,8 @@
         <v>1</v>
       </c>
       <c r="H30" s="61">
-        <f>H29+0.2</f>
-        <v>1.0649999999999999</v>
+        <f>6.7-6.4</f>
+        <v>0.29999999999999982</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -11384,8 +11384,8 @@
         <v>1</v>
       </c>
       <c r="H31" s="63">
-        <f>H30+0.2</f>
-        <v>1.2649999999999999</v>
+        <f>7-6.7</f>
+        <v>0.29999999999999982</v>
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
@@ -11409,8 +11409,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="61">
-        <f>+H33</f>
-        <v>2.14</v>
+        <v>0.7</v>
       </c>
       <c r="I32" s="2">
         <v>3</v>
@@ -11559,7 +11558,11 @@
   <dimension ref="B2:R31"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
@@ -12270,9 +12273,9 @@
     <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.26953125" customWidth="1"/>
     <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" customWidth="1"/>
     <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="38.54296875" bestFit="1" customWidth="1"/>
   </cols>
@@ -12506,7 +12509,7 @@
         <v>142</v>
       </c>
       <c r="H9" s="2">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>15</v>
@@ -12546,7 +12549,7 @@
         <v>142</v>
       </c>
       <c r="H10" s="2">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>15</v>
@@ -13684,7 +13687,7 @@
       </c>
       <c r="J6" s="29">
         <f>1+C10</f>
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -13722,7 +13725,7 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M7" s="2">
         <v>5</v>
@@ -13747,7 +13750,7 @@
         <v>229</v>
       </c>
       <c r="C10" s="11">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
         <v>20</v>
@@ -13940,13 +13943,14 @@
         <v>15</v>
       </c>
       <c r="J7" s="26">
-        <v>4</v>
+        <f t="shared" ref="J7:J25" si="1">1+$K30</f>
+        <v>1.8</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
       <c r="L7" s="16">
-        <f>-$B$59*L30/1000</f>
+        <f t="shared" ref="L7:L11" si="2">-$B$59*L30/1000</f>
         <v>-24.2242</v>
       </c>
       <c r="M7" s="2">
@@ -13980,14 +13984,14 @@
         <v>15</v>
       </c>
       <c r="J8" s="26">
-        <f t="shared" ref="J8:J25" si="1">1+$K31</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="16">
-        <f t="shared" ref="L8:L11" si="2">-$B$59*L31/1000</f>
+        <f t="shared" si="2"/>
         <v>-24.2242</v>
       </c>
       <c r="M8" s="2">
@@ -14145,7 +14149,7 @@
       </c>
       <c r="J12" s="26">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
@@ -14309,7 +14313,7 @@
       </c>
       <c r="J16" s="26">
         <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
@@ -14514,7 +14518,7 @@
       </c>
       <c r="J21" s="26">
         <f t="shared" si="1"/>
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2">
         <v>1</v>
@@ -14738,7 +14742,7 @@
         <v>130</v>
       </c>
       <c r="K30" s="11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L30" s="11">
         <v>0.2</v>
@@ -14877,7 +14881,7 @@
         <v>129</v>
       </c>
       <c r="K35" s="11">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L35" s="11">
         <v>0.2</v>
@@ -14987,7 +14991,7 @@
         <v>129</v>
       </c>
       <c r="K39" s="11">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="11">
         <v>0.25</v>
@@ -15087,7 +15091,7 @@
         <v>129</v>
       </c>
       <c r="K44" s="11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L44" s="11">
         <v>0.25</v>
